--- a/output/tables/table_2_winter_2.0.xlsx
+++ b/output/tables/table_2_winter_2.0.xlsx
@@ -1,21 +1,230 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conireds/PM2.5_Inequalities_Chile/output/tables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C121656-3A42-E84C-8A81-0454ED4A7B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="21800" yWindow="3380" windowWidth="16100" windowHeight="14520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="66">
+  <si>
+    <t>comuna</t>
+  </si>
+  <si>
+    <t>anio</t>
+  </si>
+  <si>
+    <t>N_days</t>
+  </si>
+  <si>
+    <t>Meses_validos_periodo</t>
+  </si>
+  <si>
+    <t>Conforme</t>
+  </si>
+  <si>
+    <t>Imputado</t>
+  </si>
+  <si>
+    <t>Motivo_no_conforme</t>
+  </si>
+  <si>
+    <t>Mean (SD)</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>P98</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>Cerrillos</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>46.3 (19.3)</t>
+  </si>
+  <si>
+    <t>0.015 *</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>39.4 (17.6)</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>41.1 (20.7)</t>
+  </si>
+  <si>
+    <t>Cerro Navia</t>
+  </si>
+  <si>
+    <t>48.3 (20.1)</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>42.7 (21.3)</t>
+  </si>
+  <si>
+    <t>48.2 (27)</t>
+  </si>
+  <si>
+    <t>El Bosque</t>
+  </si>
+  <si>
+    <t>49.2 (20.9)</t>
+  </si>
+  <si>
+    <t>0.003 *</t>
+  </si>
+  <si>
+    <t>40.6 (17)</t>
+  </si>
+  <si>
+    <t>43.2 (20.8)</t>
+  </si>
+  <si>
+    <t>La Florida</t>
+  </si>
+  <si>
+    <t>42.6 (17)</t>
+  </si>
+  <si>
+    <t>&lt; 0.001 *</t>
+  </si>
+  <si>
+    <t>35.4 (14.6)</t>
+  </si>
+  <si>
+    <t>33.6 (14.8)</t>
+  </si>
+  <si>
+    <t>Las Condes</t>
+  </si>
+  <si>
+    <t>27.7 (13.6)</t>
+  </si>
+  <si>
+    <t>0.009 *</t>
+  </si>
+  <si>
+    <t>23 (9.7)</t>
+  </si>
+  <si>
+    <t>Falta 1 mes de invierno (mes 6) bajo 75% de cobertura</t>
+  </si>
+  <si>
+    <t>24.2 (12)</t>
+  </si>
+  <si>
+    <t>Parque O'Higgins</t>
+  </si>
+  <si>
+    <t>40 (16.7)</t>
+  </si>
+  <si>
+    <t>0.026 *</t>
+  </si>
+  <si>
+    <t>35.3 (15.6)</t>
+  </si>
+  <si>
+    <t>Falta 1 mes de invierno (mes 8) bajo 75% de cobertura</t>
+  </si>
+  <si>
+    <t>34.6 (17.2)</t>
+  </si>
+  <si>
+    <t>Pudahuel</t>
+  </si>
+  <si>
+    <t>44.4 (19.1)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>41.6 (21.1)</t>
+  </si>
+  <si>
+    <t>45.3 (25)</t>
+  </si>
+  <si>
+    <t>Puente Alto</t>
+  </si>
+  <si>
+    <t>34.1 (15)</t>
+  </si>
+  <si>
+    <t>27.5 (11.9)</t>
+  </si>
+  <si>
+    <t>29.5 (14.1)</t>
+  </si>
+  <si>
+    <t>Quilicura</t>
+  </si>
+  <si>
+    <t>42.4 (18.1)</t>
+  </si>
+  <si>
+    <t>0.001 *</t>
+  </si>
+  <si>
+    <t>34.7 (15.7)</t>
+  </si>
+  <si>
+    <t>36.3 (17.6)</t>
+  </si>
+  <si>
+    <t>Talagante</t>
+  </si>
+  <si>
+    <t>40.8 (18.6)</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>36.3 (17.7)</t>
+  </si>
+  <si>
+    <t>36.4 (19.8)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +272,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +324,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +358,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +393,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,82 +569,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>comuna</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>anio</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>N_days</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Meses_validos_periodo</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Imputado</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Motivo_no_conforme</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Mean (SD)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>P98</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
       </c>
       <c r="C2">
         <v>119</v>
@@ -436,10 +633,8 @@
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>46.3 (19.3)</t>
-        </is>
+      <c r="H2" t="s">
+        <v>14</v>
       </c>
       <c r="I2">
         <v>7</v>
@@ -450,22 +645,16 @@
       <c r="K2">
         <v>87</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.015 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
         <v>120</v>
@@ -476,36 +665,28 @@
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>39.4 (17.6)</t>
-        </is>
+      <c r="H3" t="s">
+        <v>17</v>
       </c>
       <c r="I3">
         <v>3.6</v>
       </c>
       <c r="J3">
-        <v>91.40000000000001</v>
+        <v>91.4</v>
       </c>
       <c r="K3">
         <v>77.3</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.015 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
       </c>
       <c r="C4">
         <v>115</v>
@@ -516,10 +697,8 @@
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>41.1 (20.7)</t>
-        </is>
+      <c r="H4" t="s">
+        <v>19</v>
       </c>
       <c r="I4">
         <v>5.9</v>
@@ -528,24 +707,18 @@
         <v>114.7</v>
       </c>
       <c r="K4">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.015 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+        <v>88.9</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
       <c r="C5">
         <v>120</v>
@@ -556,10 +729,8 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>48.3 (20.1)</t>
-        </is>
+      <c r="H5" t="s">
+        <v>21</v>
       </c>
       <c r="I5">
         <v>7.5</v>
@@ -568,24 +739,18 @@
         <v>114.6</v>
       </c>
       <c r="K5">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.102</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+        <v>94.9</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
       <c r="C6">
         <v>117</v>
@@ -596,13 +761,11 @@
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>42.7 (21.3)</t>
-        </is>
+      <c r="H6" t="s">
+        <v>23</v>
       </c>
       <c r="I6">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J6">
         <v>112</v>
@@ -610,22 +773,16 @@
       <c r="K6">
         <v>85.7</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.102</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
       </c>
       <c r="C7">
         <v>111</v>
@@ -636,36 +793,28 @@
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>48.2 (27)</t>
-        </is>
+      <c r="H7" t="s">
+        <v>24</v>
       </c>
       <c r="I7">
         <v>4.5</v>
       </c>
       <c r="J7">
-        <v>133.8</v>
+        <v>133.80000000000001</v>
       </c>
       <c r="K7">
         <v>125.2</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.102</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
       </c>
       <c r="C8">
         <v>121</v>
@@ -676,10 +825,8 @@
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>49.2 (20.9)</t>
-        </is>
+      <c r="H8" t="s">
+        <v>26</v>
       </c>
       <c r="I8">
         <v>6.4</v>
@@ -690,22 +837,16 @@
       <c r="K8">
         <v>102.1</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.003 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
         <v>120</v>
@@ -716,36 +857,28 @@
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>40.6 (17)</t>
-        </is>
+      <c r="H9" t="s">
+        <v>28</v>
       </c>
       <c r="I9">
         <v>5.5</v>
       </c>
       <c r="J9">
-        <v>79.09999999999999</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="K9">
         <v>75.2</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.003 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
       </c>
       <c r="C10">
         <v>118</v>
@@ -756,10 +889,8 @@
       <c r="E10" t="b">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>43.2 (20.8)</t>
-        </is>
+      <c r="H10" t="s">
+        <v>29</v>
       </c>
       <c r="I10">
         <v>7.4</v>
@@ -768,24 +899,18 @@
         <v>112.2</v>
       </c>
       <c r="K10">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.003 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+        <v>94.6</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
       </c>
       <c r="C11">
         <v>116</v>
@@ -796,10 +921,8 @@
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>42.6 (17)</t>
-        </is>
+      <c r="H11" t="s">
+        <v>31</v>
       </c>
       <c r="I11">
         <v>7.1</v>
@@ -808,24 +931,18 @@
         <v>96.7</v>
       </c>
       <c r="K11">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>&lt; 0.001 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+        <v>80.900000000000006</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
         <v>119</v>
@@ -836,10 +953,8 @@
       <c r="E12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>35.4 (14.6)</t>
-        </is>
+      <c r="H12" t="s">
+        <v>33</v>
       </c>
       <c r="I12">
         <v>3.2</v>
@@ -850,22 +965,16 @@
       <c r="K12">
         <v>65.3</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>&lt; 0.001 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
       </c>
       <c r="C13">
         <v>117</v>
@@ -876,36 +985,28 @@
       <c r="E13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>33.6 (14.8)</t>
-        </is>
+      <c r="H13" t="s">
+        <v>34</v>
       </c>
       <c r="I13">
         <v>4.8</v>
       </c>
       <c r="J13">
-        <v>72.90000000000001</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="K13">
         <v>66.2</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>&lt; 0.001 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
       </c>
       <c r="C14">
         <v>118</v>
@@ -916,10 +1017,8 @@
       <c r="E14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>27.7 (13.6)</t>
-        </is>
+      <c r="H14" t="s">
+        <v>36</v>
       </c>
       <c r="I14">
         <v>3.2</v>
@@ -930,22 +1029,16 @@
       <c r="K14">
         <v>53.3</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0.009 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
         <v>111</v>
@@ -956,10 +1049,8 @@
       <c r="E15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>23 (9.7)</t>
-        </is>
+      <c r="H15" t="s">
+        <v>38</v>
       </c>
       <c r="I15">
         <v>3.6</v>
@@ -970,22 +1061,16 @@
       <c r="K15">
         <v>43.9</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0.009 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
       </c>
       <c r="C16">
         <v>106</v>
@@ -996,15 +1081,11 @@
       <c r="E16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Falta 1 mes de invierno (mes 6) bajo 75% de cobertura</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>24.2 (12)</t>
-        </is>
+      <c r="G16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" t="s">
+        <v>40</v>
       </c>
       <c r="I16">
         <v>2.6</v>
@@ -1015,22 +1096,16 @@
       <c r="K16">
         <v>55</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0.009 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Parque O'Higgins</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
       </c>
       <c r="C17">
         <v>121</v>
@@ -1041,10 +1116,8 @@
       <c r="E17" t="b">
         <v>1</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>40 (16.7)</t>
-        </is>
+      <c r="H17" t="s">
+        <v>42</v>
       </c>
       <c r="I17">
         <v>6.4</v>
@@ -1053,24 +1126,18 @@
         <v>103.4</v>
       </c>
       <c r="K17">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>0.026 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Parque O'Higgins</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+        <v>74.599999999999994</v>
+      </c>
+      <c r="L17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
         <v>120</v>
@@ -1081,36 +1148,28 @@
       <c r="E18" t="b">
         <v>1</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>35.3 (15.6)</t>
-        </is>
+      <c r="H18" t="s">
+        <v>44</v>
       </c>
       <c r="I18">
         <v>2.8</v>
       </c>
       <c r="J18">
-        <v>78.40000000000001</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="K18">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0.026 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Parque O'Higgins</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+        <v>67.599999999999994</v>
+      </c>
+      <c r="L18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
       </c>
       <c r="C19">
         <v>106</v>
@@ -1121,15 +1180,11 @@
       <c r="E19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Falta 1 mes de invierno (mes 8) bajo 75% de cobertura</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>34.6 (17.2)</t>
-        </is>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
+        <v>46</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -1140,22 +1195,16 @@
       <c r="K19">
         <v>71.2</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>0.026 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
       </c>
       <c r="C20">
         <v>118</v>
@@ -1166,10 +1215,8 @@
       <c r="E20" t="b">
         <v>1</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>44.4 (19.1)</t>
-        </is>
+      <c r="H20" t="s">
+        <v>48</v>
       </c>
       <c r="I20">
         <v>5.6</v>
@@ -1180,22 +1227,16 @@
       <c r="K20">
         <v>95.2</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
       </c>
       <c r="C21">
         <v>116</v>
@@ -1206,10 +1247,8 @@
       <c r="E21" t="b">
         <v>1</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>41.6 (21.1)</t>
-        </is>
+      <c r="H21" t="s">
+        <v>50</v>
       </c>
       <c r="I21">
         <v>6.5</v>
@@ -1220,22 +1259,16 @@
       <c r="K21">
         <v>89.7</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
       </c>
       <c r="C22">
         <v>106</v>
@@ -1246,15 +1279,11 @@
       <c r="E22" t="b">
         <v>1</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Falta 1 mes de invierno (mes 8) bajo 75% de cobertura</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>45.3 (25)</t>
-        </is>
+      <c r="G22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" t="s">
+        <v>51</v>
       </c>
       <c r="I22">
         <v>5.6</v>
@@ -1265,22 +1294,16 @@
       <c r="K22">
         <v>115.3</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
       </c>
       <c r="C23">
         <v>115</v>
@@ -1291,10 +1314,8 @@
       <c r="E23" t="b">
         <v>1</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>34.1 (15)</t>
-        </is>
+      <c r="H23" t="s">
+        <v>53</v>
       </c>
       <c r="I23">
         <v>4.7</v>
@@ -1305,22 +1326,16 @@
       <c r="K23">
         <v>71</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>&lt; 0.001 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
       </c>
       <c r="C24">
         <v>119</v>
@@ -1331,10 +1346,8 @@
       <c r="E24" t="b">
         <v>1</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>27.5 (11.9)</t>
-        </is>
+      <c r="H24" t="s">
+        <v>54</v>
       </c>
       <c r="I24">
         <v>2.4</v>
@@ -1345,22 +1358,16 @@
       <c r="K24">
         <v>51</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>&lt; 0.001 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
       </c>
       <c r="C25">
         <v>117</v>
@@ -1371,10 +1378,8 @@
       <c r="E25" t="b">
         <v>1</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>29.5 (14.1)</t>
-        </is>
+      <c r="H25" t="s">
+        <v>55</v>
       </c>
       <c r="I25">
         <v>4.8</v>
@@ -1385,22 +1390,16 @@
       <c r="K25">
         <v>58.8</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>&lt; 0.001 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
       </c>
       <c r="C26">
         <v>119</v>
@@ -1411,10 +1410,8 @@
       <c r="E26" t="b">
         <v>1</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>42.4 (18.1)</t>
-        </is>
+      <c r="H26" t="s">
+        <v>57</v>
       </c>
       <c r="I26">
         <v>6.2</v>
@@ -1423,24 +1420,18 @@
         <v>103</v>
       </c>
       <c r="K26">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>0.001 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+        <v>84.4</v>
+      </c>
+      <c r="L26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
       </c>
       <c r="C27">
         <v>117</v>
@@ -1451,10 +1442,8 @@
       <c r="E27" t="b">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>34.7 (15.7)</t>
-        </is>
+      <c r="H27" t="s">
+        <v>59</v>
       </c>
       <c r="I27">
         <v>3</v>
@@ -1465,22 +1454,16 @@
       <c r="K27">
         <v>66.5</v>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0.001 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
       </c>
       <c r="C28">
         <v>113</v>
@@ -1491,36 +1474,28 @@
       <c r="E28" t="b">
         <v>1</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>36.3 (17.6)</t>
-        </is>
+      <c r="H28" t="s">
+        <v>60</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
       <c r="J28">
-        <v>78.59999999999999</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="K28">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0.001 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+        <v>69.900000000000006</v>
+      </c>
+      <c r="L28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
       </c>
       <c r="C29">
         <v>114</v>
@@ -1531,10 +1506,8 @@
       <c r="E29" t="b">
         <v>1</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>40.8 (18.6)</t>
-        </is>
+      <c r="H29" t="s">
+        <v>62</v>
       </c>
       <c r="I29">
         <v>7.9</v>
@@ -1545,22 +1518,16 @@
       <c r="K29">
         <v>86.7</v>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0.119</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
       </c>
       <c r="C30">
         <v>116</v>
@@ -1571,10 +1538,8 @@
       <c r="E30" t="b">
         <v>1</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>36.3 (17.7)</t>
-        </is>
+      <c r="H30" t="s">
+        <v>64</v>
       </c>
       <c r="I30">
         <v>5.3</v>
@@ -1583,24 +1548,18 @@
         <v>84.2</v>
       </c>
       <c r="K30">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>0.119</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+        <v>75.099999999999994</v>
+      </c>
+      <c r="L30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
       </c>
       <c r="C31">
         <v>115</v>
@@ -1611,10 +1570,8 @@
       <c r="E31" t="b">
         <v>1</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>36.4 (19.8)</t>
-        </is>
+      <c r="H31" t="s">
+        <v>65</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -1623,15 +1580,14 @@
         <v>85.3</v>
       </c>
       <c r="K31">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>0.119</t>
-        </is>
+        <v>76.900000000000006</v>
+      </c>
+      <c r="L31" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/output/tables/table_2_winter_2.0.xlsx
+++ b/output/tables/table_2_winter_2.0.xlsx
@@ -1,230 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10726"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conireds/PM2.5_Inequalities_Chile/output/tables/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C121656-3A42-E84C-8A81-0454ED4A7B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21800" yWindow="3380" windowWidth="16100" windowHeight="14520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="66">
-  <si>
-    <t>comuna</t>
-  </si>
-  <si>
-    <t>anio</t>
-  </si>
-  <si>
-    <t>N_days</t>
-  </si>
-  <si>
-    <t>Meses_validos_periodo</t>
-  </si>
-  <si>
-    <t>Conforme</t>
-  </si>
-  <si>
-    <t>Imputado</t>
-  </si>
-  <si>
-    <t>Motivo_no_conforme</t>
-  </si>
-  <si>
-    <t>Mean (SD)</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>P98</t>
-  </si>
-  <si>
-    <t>p_value</t>
-  </si>
-  <si>
-    <t>Cerrillos</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>46.3 (19.3)</t>
-  </si>
-  <si>
-    <t>0.015 *</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>39.4 (17.6)</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>41.1 (20.7)</t>
-  </si>
-  <si>
-    <t>Cerro Navia</t>
-  </si>
-  <si>
-    <t>48.3 (20.1)</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>42.7 (21.3)</t>
-  </si>
-  <si>
-    <t>48.2 (27)</t>
-  </si>
-  <si>
-    <t>El Bosque</t>
-  </si>
-  <si>
-    <t>49.2 (20.9)</t>
-  </si>
-  <si>
-    <t>0.003 *</t>
-  </si>
-  <si>
-    <t>40.6 (17)</t>
-  </si>
-  <si>
-    <t>43.2 (20.8)</t>
-  </si>
-  <si>
-    <t>La Florida</t>
-  </si>
-  <si>
-    <t>42.6 (17)</t>
-  </si>
-  <si>
-    <t>&lt; 0.001 *</t>
-  </si>
-  <si>
-    <t>35.4 (14.6)</t>
-  </si>
-  <si>
-    <t>33.6 (14.8)</t>
-  </si>
-  <si>
-    <t>Las Condes</t>
-  </si>
-  <si>
-    <t>27.7 (13.6)</t>
-  </si>
-  <si>
-    <t>0.009 *</t>
-  </si>
-  <si>
-    <t>23 (9.7)</t>
-  </si>
-  <si>
-    <t>Falta 1 mes de invierno (mes 6) bajo 75% de cobertura</t>
-  </si>
-  <si>
-    <t>24.2 (12)</t>
-  </si>
-  <si>
-    <t>Parque O'Higgins</t>
-  </si>
-  <si>
-    <t>40 (16.7)</t>
-  </si>
-  <si>
-    <t>0.026 *</t>
-  </si>
-  <si>
-    <t>35.3 (15.6)</t>
-  </si>
-  <si>
-    <t>Falta 1 mes de invierno (mes 8) bajo 75% de cobertura</t>
-  </si>
-  <si>
-    <t>34.6 (17.2)</t>
-  </si>
-  <si>
-    <t>Pudahuel</t>
-  </si>
-  <si>
-    <t>44.4 (19.1)</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>41.6 (21.1)</t>
-  </si>
-  <si>
-    <t>45.3 (25)</t>
-  </si>
-  <si>
-    <t>Puente Alto</t>
-  </si>
-  <si>
-    <t>34.1 (15)</t>
-  </si>
-  <si>
-    <t>27.5 (11.9)</t>
-  </si>
-  <si>
-    <t>29.5 (14.1)</t>
-  </si>
-  <si>
-    <t>Quilicura</t>
-  </si>
-  <si>
-    <t>42.4 (18.1)</t>
-  </si>
-  <si>
-    <t>0.001 *</t>
-  </si>
-  <si>
-    <t>34.7 (15.7)</t>
-  </si>
-  <si>
-    <t>36.3 (17.6)</t>
-  </si>
-  <si>
-    <t>Talagante</t>
-  </si>
-  <si>
-    <t>40.8 (18.6)</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>36.3 (17.7)</t>
-  </si>
-  <si>
-    <t>36.4 (19.8)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -324,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -358,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -393,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -569,60 +350,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="13.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>comuna</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N_days</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Meses_validos_periodo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imputado</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Motivo_no_conforme</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>P98</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C2">
         <v>119</v>
@@ -633,8 +436,10 @@
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>46.3 (19.3)</t>
+        </is>
       </c>
       <c r="I2">
         <v>7</v>
@@ -645,16 +450,22 @@
       <c r="K2">
         <v>87</v>
       </c>
-      <c r="L2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C3">
         <v>120</v>
@@ -665,28 +476,36 @@
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="s">
-        <v>17</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>39.4 (17.6)</t>
+        </is>
       </c>
       <c r="I3">
         <v>3.6</v>
       </c>
       <c r="J3">
-        <v>91.4</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K3">
         <v>77.3</v>
       </c>
-      <c r="L3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C4">
         <v>115</v>
@@ -697,8 +516,10 @@
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>19</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>41.1 (20.7)</t>
+        </is>
       </c>
       <c r="I4">
         <v>5.9</v>
@@ -707,18 +528,24 @@
         <v>114.7</v>
       </c>
       <c r="K4">
-        <v>88.9</v>
-      </c>
-      <c r="L4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C5">
         <v>120</v>
@@ -729,8 +556,10 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="s">
-        <v>21</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>48.3 (20.1)</t>
+        </is>
       </c>
       <c r="I5">
         <v>7.5</v>
@@ -739,18 +568,24 @@
         <v>114.6</v>
       </c>
       <c r="K5">
-        <v>94.9</v>
-      </c>
-      <c r="L5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
+        <v>94.90000000000001</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C6">
         <v>117</v>
@@ -761,11 +596,13 @@
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
-        <v>23</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>42.7 (21.3)</t>
+        </is>
       </c>
       <c r="I6">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="J6">
         <v>112</v>
@@ -773,16 +610,22 @@
       <c r="K6">
         <v>85.7</v>
       </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C7">
         <v>111</v>
@@ -793,28 +636,36 @@
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
-        <v>24</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>48.2 (27)</t>
+        </is>
       </c>
       <c r="I7">
         <v>4.5</v>
       </c>
       <c r="J7">
-        <v>133.80000000000001</v>
+        <v>133.8</v>
       </c>
       <c r="K7">
         <v>125.2</v>
       </c>
-      <c r="L7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C8">
         <v>121</v>
@@ -825,8 +676,10 @@
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" t="s">
-        <v>26</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>49.2 (20.9)</t>
+        </is>
       </c>
       <c r="I8">
         <v>6.4</v>
@@ -837,16 +690,22 @@
       <c r="K8">
         <v>102.1</v>
       </c>
-      <c r="L8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C9">
         <v>120</v>
@@ -857,28 +716,36 @@
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>28</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>40.6 (17)</t>
+        </is>
       </c>
       <c r="I9">
         <v>5.5</v>
       </c>
       <c r="J9">
-        <v>79.099999999999994</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K9">
         <v>75.2</v>
       </c>
-      <c r="L9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C10">
         <v>118</v>
@@ -889,8 +756,10 @@
       <c r="E10" t="b">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
-        <v>29</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>43.2 (20.8)</t>
+        </is>
       </c>
       <c r="I10">
         <v>7.4</v>
@@ -899,18 +768,24 @@
         <v>112.2</v>
       </c>
       <c r="K10">
-        <v>94.6</v>
-      </c>
-      <c r="L10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C11">
         <v>116</v>
@@ -921,8 +796,10 @@
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="H11" t="s">
-        <v>31</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>42.6 (17)</t>
+        </is>
       </c>
       <c r="I11">
         <v>7.1</v>
@@ -931,18 +808,24 @@
         <v>96.7</v>
       </c>
       <c r="K11">
-        <v>80.900000000000006</v>
-      </c>
-      <c r="L11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
+        <v>80.90000000000001</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C12">
         <v>119</v>
@@ -953,8 +836,10 @@
       <c r="E12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" t="s">
-        <v>33</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>35.4 (14.6)</t>
+        </is>
       </c>
       <c r="I12">
         <v>3.2</v>
@@ -965,16 +850,22 @@
       <c r="K12">
         <v>65.3</v>
       </c>
-      <c r="L12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C13">
         <v>117</v>
@@ -985,28 +876,36 @@
       <c r="E13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="s">
-        <v>34</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>33.6 (14.8)</t>
+        </is>
       </c>
       <c r="I13">
         <v>4.8</v>
       </c>
       <c r="J13">
-        <v>72.900000000000006</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K13">
         <v>66.2</v>
       </c>
-      <c r="L13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C14">
         <v>118</v>
@@ -1017,8 +916,10 @@
       <c r="E14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" t="s">
-        <v>36</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>27.7 (13.6)</t>
+        </is>
       </c>
       <c r="I14">
         <v>3.2</v>
@@ -1029,16 +930,22 @@
       <c r="K14">
         <v>53.3</v>
       </c>
-      <c r="L14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C15">
         <v>111</v>
@@ -1049,8 +956,10 @@
       <c r="E15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="s">
-        <v>38</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>23 (9.7)</t>
+        </is>
       </c>
       <c r="I15">
         <v>3.6</v>
@@ -1061,16 +970,22 @@
       <c r="K15">
         <v>43.9</v>
       </c>
-      <c r="L15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C16">
         <v>106</v>
@@ -1081,11 +996,15 @@
       <c r="E16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" t="s">
-        <v>40</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Falta 1 mes de invierno (mes 6) bajo 75% de cobertura</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>24.2 (12)</t>
+        </is>
       </c>
       <c r="I16">
         <v>2.6</v>
@@ -1096,16 +1015,22 @@
       <c r="K16">
         <v>55</v>
       </c>
-      <c r="L16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" t="s">
-        <v>13</v>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Parque O'Higgins</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C17">
         <v>121</v>
@@ -1116,8 +1041,10 @@
       <c r="E17" t="b">
         <v>1</v>
       </c>
-      <c r="H17" t="s">
-        <v>42</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>40 (16.7)</t>
+        </is>
       </c>
       <c r="I17">
         <v>6.4</v>
@@ -1126,18 +1053,24 @@
         <v>103.4</v>
       </c>
       <c r="K17">
-        <v>74.599999999999994</v>
-      </c>
-      <c r="L17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Parque O'Higgins</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C18">
         <v>120</v>
@@ -1148,28 +1081,36 @@
       <c r="E18" t="b">
         <v>1</v>
       </c>
-      <c r="H18" t="s">
-        <v>44</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>35.3 (15.6)</t>
+        </is>
       </c>
       <c r="I18">
         <v>2.8</v>
       </c>
       <c r="J18">
-        <v>78.400000000000006</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K18">
-        <v>67.599999999999994</v>
-      </c>
-      <c r="L18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Parque O'Higgins</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C19">
         <v>106</v>
@@ -1180,11 +1121,15 @@
       <c r="E19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" t="s">
-        <v>46</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Falta 1 mes de invierno (mes 8) bajo 75% de cobertura</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>34.6 (17.2)</t>
+        </is>
       </c>
       <c r="I19">
         <v>5</v>
@@ -1195,16 +1140,22 @@
       <c r="K19">
         <v>71.2</v>
       </c>
-      <c r="L19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C20">
         <v>118</v>
@@ -1215,8 +1166,10 @@
       <c r="E20" t="b">
         <v>1</v>
       </c>
-      <c r="H20" t="s">
-        <v>48</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>44.4 (19.1)</t>
+        </is>
       </c>
       <c r="I20">
         <v>5.6</v>
@@ -1227,16 +1180,22 @@
       <c r="K20">
         <v>95.2</v>
       </c>
-      <c r="L20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C21">
         <v>116</v>
@@ -1247,8 +1206,10 @@
       <c r="E21" t="b">
         <v>1</v>
       </c>
-      <c r="H21" t="s">
-        <v>50</v>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>41.6 (21.1)</t>
+        </is>
       </c>
       <c r="I21">
         <v>6.5</v>
@@ -1259,16 +1220,22 @@
       <c r="K21">
         <v>89.7</v>
       </c>
-      <c r="L21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" t="s">
-        <v>18</v>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C22">
         <v>106</v>
@@ -1279,11 +1246,15 @@
       <c r="E22" t="b">
         <v>1</v>
       </c>
-      <c r="G22" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" t="s">
-        <v>51</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Falta 1 mes de invierno (mes 8) bajo 75% de cobertura</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>45.3 (25)</t>
+        </is>
       </c>
       <c r="I22">
         <v>5.6</v>
@@ -1294,16 +1265,22 @@
       <c r="K22">
         <v>115.3</v>
       </c>
-      <c r="L22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C23">
         <v>115</v>
@@ -1314,8 +1291,10 @@
       <c r="E23" t="b">
         <v>1</v>
       </c>
-      <c r="H23" t="s">
-        <v>53</v>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>34.1 (15)</t>
+        </is>
       </c>
       <c r="I23">
         <v>4.7</v>
@@ -1326,16 +1305,22 @@
       <c r="K23">
         <v>71</v>
       </c>
-      <c r="L23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C24">
         <v>119</v>
@@ -1346,8 +1331,10 @@
       <c r="E24" t="b">
         <v>1</v>
       </c>
-      <c r="H24" t="s">
-        <v>54</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>27.5 (11.9)</t>
+        </is>
       </c>
       <c r="I24">
         <v>2.4</v>
@@ -1358,16 +1345,22 @@
       <c r="K24">
         <v>51</v>
       </c>
-      <c r="L24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>18</v>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C25">
         <v>117</v>
@@ -1378,8 +1371,10 @@
       <c r="E25" t="b">
         <v>1</v>
       </c>
-      <c r="H25" t="s">
-        <v>55</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>29.5 (14.1)</t>
+        </is>
       </c>
       <c r="I25">
         <v>4.8</v>
@@ -1390,16 +1385,22 @@
       <c r="K25">
         <v>58.8</v>
       </c>
-      <c r="L25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C26">
         <v>119</v>
@@ -1410,8 +1411,10 @@
       <c r="E26" t="b">
         <v>1</v>
       </c>
-      <c r="H26" t="s">
-        <v>57</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>42.4 (18.1)</t>
+        </is>
       </c>
       <c r="I26">
         <v>6.2</v>
@@ -1420,18 +1423,24 @@
         <v>103</v>
       </c>
       <c r="K26">
-        <v>84.4</v>
-      </c>
-      <c r="L26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C27">
         <v>117</v>
@@ -1442,8 +1451,10 @@
       <c r="E27" t="b">
         <v>1</v>
       </c>
-      <c r="H27" t="s">
-        <v>59</v>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>34.7 (15.7)</t>
+        </is>
       </c>
       <c r="I27">
         <v>3</v>
@@ -1454,16 +1465,22 @@
       <c r="K27">
         <v>66.5</v>
       </c>
-      <c r="L27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" t="s">
-        <v>18</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C28">
         <v>113</v>
@@ -1474,28 +1491,36 @@
       <c r="E28" t="b">
         <v>1</v>
       </c>
-      <c r="H28" t="s">
-        <v>60</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>36.3 (17.6)</t>
+        </is>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
       <c r="J28">
-        <v>78.599999999999994</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K28">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="L28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" t="s">
-        <v>13</v>
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="C29">
         <v>114</v>
@@ -1506,8 +1531,10 @@
       <c r="E29" t="b">
         <v>1</v>
       </c>
-      <c r="H29" t="s">
-        <v>62</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>40.8 (18.6)</t>
+        </is>
       </c>
       <c r="I29">
         <v>7.9</v>
@@ -1518,16 +1545,22 @@
       <c r="K29">
         <v>86.7</v>
       </c>
-      <c r="L29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="C30">
         <v>116</v>
@@ -1538,8 +1571,10 @@
       <c r="E30" t="b">
         <v>1</v>
       </c>
-      <c r="H30" t="s">
-        <v>64</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>36.3 (17.7)</t>
+        </is>
       </c>
       <c r="I30">
         <v>5.3</v>
@@ -1548,18 +1583,24 @@
         <v>84.2</v>
       </c>
       <c r="K30">
-        <v>75.099999999999994</v>
-      </c>
-      <c r="L30" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" t="s">
-        <v>18</v>
+        <v>75.09999999999999</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="C31">
         <v>115</v>
@@ -1570,8 +1611,10 @@
       <c r="E31" t="b">
         <v>1</v>
       </c>
-      <c r="H31" t="s">
-        <v>65</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>36.4 (19.8)</t>
+        </is>
       </c>
       <c r="I31">
         <v>6</v>
@@ -1580,14 +1623,15 @@
         <v>85.3</v>
       </c>
       <c r="K31">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="L31" t="s">
-        <v>63</v>
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>